--- a/artfynd/A 8659-2025 artfynd.xlsx
+++ b/artfynd/A 8659-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89159050</v>
+        <v>137321878</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>58468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,34 +713,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Älghultssjön, Vg</t>
+          <t>Ekeskogen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346819</v>
+        <v>346511</v>
       </c>
       <c r="R2" t="n">
-        <v>6441271</v>
+        <v>6441250</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,12 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-13</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-13</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,24 +783,388 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Inger Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kaj Svahn, Tim Hipkiss</t>
+          <t>Inger Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137321878</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>89159050</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S Älghultssjön, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>346819</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6441271</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-04-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-04-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kaj Svahn, Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/89159050</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137321875</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58189</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ekeskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>346511</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6441250</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inger Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inger Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137321875</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137321880</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58654</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ekeskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>346511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6441250</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inger Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inger Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137321880</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8659-2025 artfynd.xlsx
+++ b/artfynd/A 8659-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137321878</v>
       </c>
       <c r="B2" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>137321875</v>
       </c>
       <c r="B4" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>137321880</v>
       </c>
       <c r="B5" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8659-2025 artfynd.xlsx
+++ b/artfynd/A 8659-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137321878</v>
       </c>
       <c r="B2" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>137321875</v>
       </c>
       <c r="B4" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>137321880</v>
       </c>
       <c r="B5" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8659-2025 artfynd.xlsx
+++ b/artfynd/A 8659-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137321878</v>
       </c>
       <c r="B2" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>137321875</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>137321880</v>
       </c>
       <c r="B5" t="n">
-        <v>58658</v>
+        <v>58661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
